--- a/src/media/excel/雨量_注意_新潟デモ2更新結果.xlsx
+++ b/src/media/excel/雨量_注意_新潟デモ2更新結果.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20250921-034</t>
+          <t>20250921-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -485,6 +485,80 @@
         </is>
       </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t>自治体</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20250921-002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025/09/21 11:40</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>１０分雨量</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>大湯</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>信濃川</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>信濃川河川事務所</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>国河川</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20250921-003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025/09/21 11:50</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>１０分雨量</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>東野</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>北陸その他</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>羽咋土木事務所</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>自治体</t>
         </is>

--- a/src/media/excel/雨量_注意_新潟デモ2更新結果.xlsx
+++ b/src/media/excel/雨量_注意_新潟デモ2更新結果.xlsx
@@ -456,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20250921-001</t>
+          <t>20250921-035</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20250921-002</t>
+          <t>20250921-036</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -530,7 +530,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20250921-003</t>
+          <t>20250921-037</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
